--- a/branches/release-please--branches--main/StructureDefinition-ph-core-name.xlsx
+++ b/branches/release-please--branches--main/StructureDefinition-ph-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:47:01+00:00</t>
+    <t>2026-06-17T13:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
